--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,210 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120463321</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gräsflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576506</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7014954</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120463320</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gräsflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576506</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7014954</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120463321</v>
+        <v>120463320</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120463320</v>
+        <v>120463321</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120463320</v>
+        <v>120463321</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120463321</v>
+        <v>120463320</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,122 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121547491</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100967</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Myrbräcka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Saxifraga hirculus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kultaflon, vid bäckens början, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576404</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7015334</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Y-Sol-0131</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Observatör: Bergvall, Frans</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>121547491</v>
       </c>
       <c r="B7" t="n">
-        <v>100967</v>
+        <v>100972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>121547491</v>
       </c>
       <c r="B7" t="n">
-        <v>100972</v>
+        <v>100973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>121547491</v>
       </c>
       <c r="B7" t="n">
-        <v>100973</v>
+        <v>100981</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80470823</v>
+        <v>120463321</v>
       </c>
       <c r="B4" t="n">
-        <v>99113</v>
+        <v>79706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,45 +927,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1448</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myrbräcka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxifraga hirculus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kultaflon, vid bäckens början, Ång</t>
+          <t>Gräsflon, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576403.7542073439</v>
+        <v>576506</v>
       </c>
       <c r="R4" t="n">
-        <v>7015334.225743412</v>
+        <v>7014954</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,34 +983,14 @@
           <t>Helgum</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Y-Sol-0131</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kultraflohalsen lång myrarm vid Kultraflobäckens början SO Kultraflon rikl (Bergv. 1985 r.). /Ångermanlands flora</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,33 +999,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Noel Wieser</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120463321</v>
+        <v>120463320</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79671</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1145,224 +1116,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120463320</v>
-      </c>
-      <c r="B6" t="n">
-        <v>79671</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Gräsflon, Ång</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>576506</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7014954</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>121547491</v>
-      </c>
-      <c r="B7" t="n">
-        <v>100981</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1448</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Myrbräcka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Saxifraga hirculus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Kultaflon, vid bäckens början, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>576404</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7015334</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Y-Sol-0131</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Bergvall, Frans</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Via Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80043841</v>
+        <v>80470823</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>1448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Myrbräcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Saxifraga hirculus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kultaflon, SO delen, Ång</t>
+          <t>Kultaflon, vid bäckens början, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576404.205099025</v>
+        <v>576404</v>
       </c>
       <c r="R2" t="n">
-        <v>7015334.236442299</v>
+        <v>7015334</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -739,29 +742,24 @@
           <t>Helgum</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Sol-0062</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid Kultaflobäckens början. Många små delvis underjordiska bäckar.Kan vara gammal slåttermark men nu igenväxt. Rikare mark.</t>
+          <t>Kultraflohalsen lång myrarm vid Kultraflobäckens början SO Kultraflon rikl (Bergv. 1985 r.). /Ångermanlands flora</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,38 +768,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Rikare sumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Monica Svensson, Sören Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80043839</v>
+        <v>120463320</v>
       </c>
       <c r="B3" t="n">
-        <v>99113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1448</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myrbräcka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxifraga hirculus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kultaflon, SO delen, Ång</t>
+          <t>Gräsflon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576404.205099025</v>
+        <v>576506</v>
       </c>
       <c r="R3" t="n">
-        <v>7015334.236442299</v>
+        <v>7014954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,52 +856,32 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vid Kultaflobäckens början. Många små delvis underjordiska bäckar.Kan vara gammal slåttermark men nu igenväxt. Rikare mark.</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Rikare sumpskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Monica Svensson, Sören Svensson</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -918,12 +891,7 @@
         <v>120463321</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,50 +985,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120463320</v>
+        <v>80043841</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsflon, Ång</t>
+          <t>Kultaflon, SO delen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576506</v>
+        <v>576404</v>
       </c>
       <c r="R5" t="n">
-        <v>7014954</v>
+        <v>7015334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,12 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2019-08-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2019-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid Kultaflobäckens början. Många små delvis underjordiska bäckar.Kan vara gammal slåttermark men nu igenväxt. Rikare mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,16 +1067,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rikare sumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Jan Yngve Andersson, Monica Svensson, Sören Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 53130-2022 artfynd.xlsx
+++ b/artfynd/A 53130-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80470823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463320</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120463321</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,8 +1105,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80043841</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>